--- a/Sample_4_School_Class_Teacher.xlsx
+++ b/Sample_4_School_Class_Teacher.xlsx
@@ -461,11 +461,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -659,7 +661,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Test 1</t>
+          <t>Test 1 Name</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -667,124 +669,364 @@
           <t>Unit Test 1</t>
         </is>
       </c>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Test 2</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Mid-Term</t>
-        </is>
-      </c>
+          <t>Test 1 Date</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Test 3</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Unit Test 2</t>
-        </is>
-      </c>
+          <t>Max Marks - Mathematics (Test 1)</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Test 4</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Final Exam</t>
-        </is>
-      </c>
+          <t>Max Marks - Science (Test 1)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SCORING CONFIG</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="n"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - English (Test 1)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Pass Threshold %</t>
+          <t>Max Marks - Kannada (Test 1)</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Absent Alert (days)</t>
+          <t>Max Marks - Social Studies (Test 1)</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Drop Alert %</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>20</v>
+          <t>Test 2 Name</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Mid-Term</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Display Marks</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Test 2 Date</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Display Percentage</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>Max Marks - Mathematics (Test 2)</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Display Grade</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>Max Marks - Science (Test 2)</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>Max Marks - English (Test 2)</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - Kannada (Test 2)</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - Social Studies (Test 2)</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Test 3 Name</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Unit Test 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Test 3 Date</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - Mathematics (Test 3)</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - Science (Test 3)</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - English (Test 3)</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - Kannada (Test 3)</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - Social Studies (Test 3)</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Test 4 Name</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Final Exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Test 4 Date</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - Mathematics (Test 4)</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - Science (Test 4)</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - English (Test 4)</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - Kannada (Test 4)</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Max Marks - Social Studies (Test 4)</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>SCORING CONFIG</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Pass Threshold %</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Absent Alert (days)</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Drop Alert %</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Display Marks</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Display Percentage</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Display Grade</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
           <t>Display Pass/Fail</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1028,7 +1270,6 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>89</v>
       </c>
@@ -1047,7 +1288,6 @@
       <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
         <v>47</v>
       </c>
@@ -1066,7 +1306,6 @@
       <c r="W2" t="n">
         <v>0</v>
       </c>
-      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
         <v>93</v>
       </c>
@@ -1125,7 +1364,6 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
         <v>77</v>
       </c>
@@ -1144,7 +1382,6 @@
       <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
         <v>41</v>
       </c>
@@ -1163,7 +1400,6 @@
       <c r="W3" t="n">
         <v>0</v>
       </c>
-      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
         <v>86</v>
       </c>
@@ -1222,7 +1458,6 @@
       <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
         <v>66</v>
       </c>
@@ -1241,7 +1476,6 @@
       <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
         <v>35</v>
       </c>
@@ -1260,7 +1494,6 @@
       <c r="W4" t="n">
         <v>0</v>
       </c>
-      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
         <v>70</v>
       </c>
@@ -1319,7 +1552,6 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
         <v>62</v>
       </c>
@@ -1338,7 +1570,6 @@
       <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
         <v>27</v>
       </c>
@@ -1357,7 +1588,6 @@
       <c r="W5" t="n">
         <v>0</v>
       </c>
-      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
         <v>50</v>
       </c>
@@ -1416,7 +1646,6 @@
       <c r="I6" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
         <v>55</v>
       </c>
@@ -1435,7 +1664,6 @@
       <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
         <v>29</v>
       </c>
@@ -1454,7 +1682,6 @@
       <c r="W6" t="n">
         <v>0</v>
       </c>
-      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
         <v>61</v>
       </c>
@@ -1513,7 +1740,6 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
         <v>37</v>
       </c>
@@ -1532,7 +1758,6 @@
       <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
         <v>19</v>
       </c>
@@ -1551,7 +1776,6 @@
       <c r="W7" t="n">
         <v>0</v>
       </c>
-      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="n">
         <v>32</v>
       </c>
@@ -1610,7 +1834,6 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
         <v>36</v>
       </c>
@@ -1629,7 +1852,6 @@
       <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
         <v>21</v>
       </c>
@@ -1648,7 +1870,6 @@
       <c r="W8" t="n">
         <v>0</v>
       </c>
-      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="n">
         <v>51</v>
       </c>
@@ -1707,7 +1928,6 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
         <v>16</v>
       </c>
@@ -1726,7 +1946,6 @@
       <c r="P9" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
         <v>6</v>
       </c>
@@ -1745,7 +1964,6 @@
       <c r="W9" t="n">
         <v>1</v>
       </c>
-      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="n">
         <v>9</v>
       </c>
@@ -1794,7 +2012,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1802,7 +2019,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -1817,7 +2033,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -1825,7 +2040,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
